--- a/mech_elec_ai_calculator/outputs/工程量清单_agnesai.xlsx
+++ b/mech_elec_ai_calculator/outputs/工程量清单_agnesai.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>电气设备</t>
+          <t>电动机/水泵/风机</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -570,7 +570,12 @@
           <t>equipment</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+[AUDIT] ‘电气设备’分类过于笼统，图纸中明确识别出MCC-1, 电机-1, M-1, 水泵, 风机。应分别列项以便准确计价。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -624,7 +629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>断路器/隔离开关</t>
+          <t>开关</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -652,12 +657,7 @@
           <t>switch</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-[AUDIT] 识别到的MCB-1P, QF1等为微型断路器或框架断路器，属于配电柜/箱内部元件或独立开关，与'单极/双极开关'（照明控制）性质不同，建议分开列项。</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -869,7 +869,7 @@
       <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">
-[AUDIT] 图纸图层中有'E-桥架'，但清单中桥架长度19300米与线缆长度（若为米）比例失调，且未区分不同规格（如槽式、梯式）及高度。</t>
+[AUDIT] 虽然列出了桥架，但考虑到线缆长度异常，桥架长度也需同步复核。此外，未区分主桥架与分支桥架，也未提及桥架附件（弯头、三通等）。</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DL001</t>
+          <t>DL999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>电动机/水泵/风机</t>
+          <t>电力电缆终端头</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -984,7 +984,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[AUDIT] 分类过于笼统。识别到的MCC-1, 电机-1, M-1, 水泵, 风机应具体区分，以便准确计算配套的控制回路及接线工作量。</t>
+          <t>[AUDIT] 仅有4个电缆头无法覆盖72312米的电力电缆。通常每根电缆两端均需制作终端头，且中间若过长需设中间接头。即使按正常长度估算，数量也远大于4。</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>电力电缆终端头</t>
+          <t>控制电缆接线端子</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[AUDIT] 仅4个电缆头无法覆盖72312米电力电缆的需求。通常每根电缆两端均需制作终端头，且中间接头也需计入。</t>
+          <t>[AUDIT] 104个端子对于11012米的控制电缆来说极少。通常每个控制芯线端头都需要压接端子。</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DL999</t>
+          <t>DL001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>控制电缆接线端子</t>
+          <t>接地母线/接地极</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[AUDIT] 104个端子对于11012米控制电缆而言数量极少，通常按芯数计算。</t>
+          <t>[AUDIT] 清单中未包含接地系统相关工程量（如接地母线、接地极、测试板等），这是机电工程必不可少的部分。</t>
         </is>
       </c>
     </row>
